--- a/Aug_2026/daily Reports/Price List Custom.xlsx
+++ b/Aug_2026/daily Reports/Price List Custom.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4133A09-6A47-46A0-9387-DC661B5B1D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBB436C-D294-4961-967C-EF1B929819B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3462,6 +3462,12 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3470,12 +3476,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -12014,7 +12014,7 @@
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="9.1796875" style="61" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" customWidth="1"/>
-    <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="18" max="20" width="6.1796875" style="61" customWidth="1"/>
     <col min="21" max="21" width="5.54296875" bestFit="1" customWidth="1"/>
@@ -12104,33 +12104,33 @@
       </c>
     </row>
     <row r="6" spans="1:21 16383:16383" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="329" t="s">
+      <c r="A6" s="331" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="329"/>
-      <c r="C6" s="329" t="s">
+      <c r="B6" s="331"/>
+      <c r="C6" s="331" t="s">
         <v>90</v>
       </c>
       <c r="D6" s="274" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="329" t="s">
+      <c r="E6" s="331" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="329"/>
-      <c r="G6" s="329" t="s">
+      <c r="F6" s="331"/>
+      <c r="G6" s="331" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="329"/>
-      <c r="I6" s="329" t="s">
+      <c r="H6" s="331"/>
+      <c r="I6" s="331" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="329" t="s">
+      <c r="J6" s="331" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="329"/>
-      <c r="L6" s="329"/>
-      <c r="M6" s="329" t="s">
+      <c r="K6" s="331"/>
+      <c r="L6" s="331"/>
+      <c r="M6" s="331" t="s">
         <v>84</v>
       </c>
       <c r="N6" s="334" t="s">
@@ -12147,9 +12147,9 @@
       </c>
     </row>
     <row r="7" spans="1:21 16383:16383" ht="20" x14ac:dyDescent="0.35">
-      <c r="A7" s="329"/>
-      <c r="B7" s="329"/>
-      <c r="C7" s="329"/>
+      <c r="A7" s="331"/>
+      <c r="B7" s="331"/>
+      <c r="C7" s="331"/>
       <c r="D7" s="274" t="s">
         <v>57</v>
       </c>
@@ -12165,9 +12165,9 @@
       <c r="H7" s="274" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="329"/>
+      <c r="I7" s="331"/>
       <c r="J7" s="275">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="K7" s="274" t="s">
         <v>39</v>
@@ -12175,8 +12175,8 @@
       <c r="L7" s="274" t="s">
         <v>492</v>
       </c>
-      <c r="M7" s="329"/>
-      <c r="N7" s="329"/>
+      <c r="M7" s="331"/>
+      <c r="N7" s="331"/>
       <c r="O7" s="276">
         <f>IF(B3="Filer",0.5%,2.5%)</f>
         <v>5.0000000000000001E-3</v>
@@ -12216,21 +12216,19 @@
         <f>VLOOKUP(A8,'Cust. Price List'!D6:M14,10,0)</f>
         <v>52.462499999999999</v>
       </c>
-      <c r="G8" s="280">
-        <v>1</v>
-      </c>
+      <c r="G8" s="280"/>
       <c r="H8" s="280"/>
       <c r="I8" s="128">
         <f>(G8*D8)*F8+H8*F8</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J8" s="128">
         <f>I8*J7</f>
-        <v>209.85000000000002</v>
+        <v>0</v>
       </c>
       <c r="K8" s="128">
         <f>$I8*3.5%</f>
-        <v>73.447500000000005</v>
+        <v>0</v>
       </c>
       <c r="L8" s="128">
         <f t="shared" ref="L8:L13" si="0">$I8*T8</f>
@@ -12238,19 +12236,19 @@
       </c>
       <c r="M8" s="213">
         <f>I8-SUM(J8:L8)</f>
-        <v>1815.2024999999999</v>
+        <v>0</v>
       </c>
       <c r="N8" s="128">
         <f>+(G8*D8+H8)*9.92</f>
-        <v>396.8</v>
+        <v>0</v>
       </c>
       <c r="O8" s="128">
         <f t="shared" ref="O8:O14" si="1">(N8+M8)*$O$7</f>
-        <v>11.060012500000001</v>
+        <v>0</v>
       </c>
       <c r="P8" s="128">
         <f>M8+N8+O8</f>
-        <v>2223.0625125000001</v>
+        <v>0</v>
       </c>
       <c r="R8" s="216"/>
       <c r="S8" s="247"/>
@@ -12413,21 +12411,21 @@
         <f>VLOOKUP(A11,'Cust. Price List'!D9:M17,10,0)</f>
         <v>72.64</v>
       </c>
-      <c r="G11" s="280">
+      <c r="G11" s="280"/>
+      <c r="H11" s="280">
         <v>1</v>
       </c>
-      <c r="H11" s="280"/>
       <c r="I11" s="128">
         <f t="shared" si="7"/>
-        <v>2905.6</v>
+        <v>72.64</v>
       </c>
       <c r="J11" s="128">
         <f>I11*J7</f>
-        <v>290.56</v>
+        <v>11.622400000000001</v>
       </c>
       <c r="K11" s="128">
         <f t="shared" si="3"/>
-        <v>101.69600000000001</v>
+        <v>2.5424000000000002</v>
       </c>
       <c r="L11" s="128">
         <f t="shared" si="0"/>
@@ -12435,19 +12433,19 @@
       </c>
       <c r="M11" s="213">
         <f t="shared" si="4"/>
-        <v>2513.3440000000001</v>
+        <v>58.475200000000001</v>
       </c>
       <c r="N11" s="128">
         <f>+(G11*D11+H11)*13.73</f>
-        <v>549.20000000000005</v>
+        <v>13.73</v>
       </c>
       <c r="O11" s="128">
         <f t="shared" si="1"/>
-        <v>15.312719999999999</v>
+        <v>0.36102600000000001</v>
       </c>
       <c r="P11" s="128">
         <f t="shared" si="6"/>
-        <v>3077.8567199999998</v>
+        <v>72.566226</v>
       </c>
       <c r="R11" s="267"/>
       <c r="S11" s="268"/>
@@ -12604,41 +12602,39 @@
         <f>VLOOKUP(A14,'Cust. Price List'!D12:M20,10,0)</f>
         <v>39.230000000000004</v>
       </c>
-      <c r="G14" s="280">
-        <v>1</v>
-      </c>
+      <c r="G14" s="280"/>
       <c r="H14" s="280"/>
       <c r="I14" s="128">
         <f t="shared" si="2"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J14" s="128">
         <f>I14*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="K14" s="128">
         <f t="shared" si="3"/>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L14" s="128">
         <f>$I14*5.1%</f>
-        <v>80.029200000000003</v>
+        <v>0</v>
       </c>
       <c r="M14" s="213">
         <f t="shared" si="4"/>
-        <v>1355.7888000000003</v>
+        <v>0</v>
       </c>
       <c r="N14" s="128">
         <f>+(G14*D14+H14)*7.63</f>
-        <v>305.2</v>
+        <v>0</v>
       </c>
       <c r="O14" s="128">
         <f t="shared" si="1"/>
-        <v>8.3049440000000025</v>
+        <v>0</v>
       </c>
       <c r="P14" s="128">
         <f t="shared" si="6"/>
-        <v>1669.2937440000003</v>
+        <v>0</v>
       </c>
       <c r="R14" s="267"/>
       <c r="S14" s="268"/>
@@ -12659,43 +12655,43 @@
       <c r="F15" s="326"/>
       <c r="G15" s="281">
         <f t="shared" ref="G15:P15" si="9">SUM(G8:G14)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H15" s="281">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="282">
         <f t="shared" si="9"/>
-        <v>6573.3000000000011</v>
+        <v>72.64</v>
       </c>
       <c r="J15" s="282">
         <f t="shared" si="9"/>
-        <v>578.87</v>
+        <v>11.622400000000001</v>
       </c>
       <c r="K15" s="282">
         <f t="shared" si="9"/>
-        <v>230.06550000000004</v>
+        <v>2.5424000000000002</v>
       </c>
       <c r="L15" s="282">
         <f t="shared" si="9"/>
-        <v>80.029200000000003</v>
+        <v>0</v>
       </c>
       <c r="M15" s="281">
         <f t="shared" si="9"/>
-        <v>5684.3353000000006</v>
+        <v>58.475200000000001</v>
       </c>
       <c r="N15" s="281">
         <f t="shared" si="9"/>
-        <v>1251.2</v>
+        <v>13.73</v>
       </c>
       <c r="O15" s="283">
         <f t="shared" si="9"/>
-        <v>34.677676500000004</v>
+        <v>0.36102600000000001</v>
       </c>
       <c r="P15" s="281">
         <f t="shared" si="9"/>
-        <v>6970.2129765000009</v>
+        <v>72.566226</v>
       </c>
     </row>
     <row r="16" spans="1:21 16383:16383" x14ac:dyDescent="0.35">
@@ -12739,13 +12735,13 @@
       <c r="J18" s="317"/>
       <c r="K18" s="317"/>
       <c r="L18" s="318"/>
-      <c r="N18" s="330" t="s">
+      <c r="N18" s="332" t="s">
         <v>60</v>
       </c>
-      <c r="O18" s="331"/>
+      <c r="O18" s="333"/>
       <c r="P18" s="139">
         <f>I15</f>
-        <v>6573.3000000000011</v>
+        <v>72.64</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12766,7 +12762,7 @@
       <c r="O19" s="326"/>
       <c r="P19" s="140">
         <f>+J15</f>
-        <v>578.87</v>
+        <v>11.622400000000001</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12787,7 +12783,7 @@
       <c r="O20" s="326"/>
       <c r="P20" s="140">
         <f>+K15+L15</f>
-        <v>310.09470000000005</v>
+        <v>2.5424000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12809,7 +12805,7 @@
       <c r="O21" s="326"/>
       <c r="P21" s="140">
         <f>P18-P19-P20</f>
-        <v>5684.3353000000016</v>
+        <v>58.475200000000001</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12833,7 +12829,7 @@
       </c>
       <c r="P22" s="140">
         <f>+N15</f>
-        <v>1251.2</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -12849,13 +12845,13 @@
       <c r="K23" s="320"/>
       <c r="L23" s="321"/>
       <c r="M23" s="131"/>
-      <c r="N23" s="332" t="s">
+      <c r="N23" s="329" t="s">
         <v>76</v>
       </c>
-      <c r="O23" s="333"/>
+      <c r="O23" s="330"/>
       <c r="P23" s="140">
         <f>P21+P22</f>
-        <v>6935.5353000000014</v>
+        <v>72.205200000000005</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -12880,7 +12876,7 @@
       </c>
       <c r="P24" s="140">
         <f>O24*P23</f>
-        <v>34.677676500000011</v>
+        <v>0.36102600000000001</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -12890,7 +12886,7 @@
       <c r="O25" s="328"/>
       <c r="P25" s="272">
         <f>+P23+P24</f>
-        <v>6970.2129765000018</v>
+        <v>72.566226</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -13022,7 +13018,7 @@
       <c r="L4" s="310"/>
       <c r="M4" s="351">
         <f ca="1">TODAY()+1</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="N4" s="351"/>
       <c r="O4" s="351"/>
@@ -13050,7 +13046,7 @@
       <c r="L5" s="310"/>
       <c r="M5" s="351">
         <f ca="1">M4-1</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="N5" s="308"/>
       <c r="O5" s="308"/>
@@ -13923,10 +13919,10 @@
       <c r="I28" s="317"/>
       <c r="J28" s="317"/>
       <c r="K28" s="318"/>
-      <c r="M28" s="330" t="s">
+      <c r="M28" s="332" t="s">
         <v>60</v>
       </c>
-      <c r="N28" s="331"/>
+      <c r="N28" s="333"/>
       <c r="O28" s="139">
         <f>I25</f>
         <v>1452.8</v>
@@ -14029,10 +14025,10 @@
       <c r="J33" s="320"/>
       <c r="K33" s="321"/>
       <c r="L33" s="131"/>
-      <c r="M33" s="332" t="s">
+      <c r="M33" s="329" t="s">
         <v>76</v>
       </c>
-      <c r="N33" s="333"/>
+      <c r="N33" s="330"/>
       <c r="O33" s="140">
         <f>O31+O32</f>
         <v>1710.3814400000001</v>
